--- a/02_DIA_inicio_2026_analisis_assets/rbd_9719_escuela-basica-santa-olga-de-kiev_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9719_escuela-basica-santa-olga-de-kiev_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A01771E-4704-45AC-B365-5B09D85F24C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F09581F3-66EC-4C56-AA6F-B005F13CEE8E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF63F304-9BCE-4BAF-8FAD-8A0D6FFDFB2C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3057BE25-9765-43B5-8893-F2241A908425}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E212431C-B72C-48E9-84BF-A1A04F547FEC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6149990C-EAD2-414E-91A6-4BD4C026BC55}"/>
 </file>